--- a/reports/一级子公司A_现金流量表_2026-09.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-09.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>160278300</v>
+        <v>157758714</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1360814988</v>
+        <v>1343026086</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3155393</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>27283418</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1565659</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>13639772</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>790096</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>6825468</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>625874</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>5452685</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>473864</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>4097097</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>313377</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>2725661</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>236404</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2048611</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>157136</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1363094</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>392764</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>3412999</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>198048</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1713561</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>124530</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1084441</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>410970</v>
+        <v>407155</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>3565654</v>
+        <v>3517719</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2920050</v>
+        <v>2867896</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>25334910</v>
+        <v>24990277</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>163609320</v>
+        <v>169066910</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>103824000</v>
+        <v>102393667</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>900796800</v>
+        <v>888956313</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1049810</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>9090391</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>783978</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>6823106</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>526274</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>4548287</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>391247</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>3409203</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>263390</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>2275572</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>196637</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1712484</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16979550</v>
+        <v>16818604</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>147317810</v>
+        <v>145506298</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8652000</v>
+        <v>8508927</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>75066400</v>
+        <v>73948462</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3568950</v>
+        <v>3526143</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>30964890</v>
+        <v>30584213</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>133024500</v>
+        <v>134458677</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>30584820</v>
+        <v>34608233</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>183825</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1668600</v>
+        <v>1648750</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1527476</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>13905000</v>
+        <v>13730759</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>934307</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>8528400</v>
+        <v>8407333</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1711301</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14214034</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>129780000</v>
+        <v>127578754</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2016563</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>18540000</v>
+        <v>18215293</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10181260</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>92700000</v>
+        <v>91251173</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>387231</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>3522600</v>
+        <v>3477902</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14601265</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12889964</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3549849</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>32445000</v>
+        <v>32046626</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5563420</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>50985000</v>
+        <v>50284529</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5617948</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>50985000</v>
+        <v>50350330</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>182136</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1668600</v>
+        <v>1645332</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9295405</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4562348</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>41715000</v>
+        <v>41129403</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4580909</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>41715000</v>
+        <v>41215360</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>732233</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>6674400</v>
+        <v>6583055</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>642595</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>5840100</v>
+        <v>5763993</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91106</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>834300</v>
+        <v>823273</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5385687</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3909718</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>21489920</v>
+        <v>25627987</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>21489920</v>
+        <v>25627987</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
